--- a/data/raw/industry_overweight.xlsx
+++ b/data/raw/industry_overweight.xlsx
@@ -1,163 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
-  <si>
-    <t>季度</t>
-  </si>
-  <si>
-    <t>农林牧渔</t>
-  </si>
-  <si>
-    <t>基础化工</t>
-  </si>
-  <si>
-    <t>钢铁</t>
-  </si>
-  <si>
-    <t>有色金属</t>
-  </si>
-  <si>
-    <t>电子</t>
-  </si>
-  <si>
-    <t>汽车</t>
-  </si>
-  <si>
-    <t>家用电器</t>
-  </si>
-  <si>
-    <t>食品饮料</t>
-  </si>
-  <si>
-    <t>纺织服饰</t>
-  </si>
-  <si>
-    <t>轻工制造</t>
-  </si>
-  <si>
-    <t>医药生物</t>
-  </si>
-  <si>
-    <t>公用事业</t>
-  </si>
-  <si>
-    <t>交通运输</t>
-  </si>
-  <si>
-    <t>房地产</t>
-  </si>
-  <si>
-    <t>商贸零售</t>
-  </si>
-  <si>
-    <t>社会服务</t>
-  </si>
-  <si>
-    <t>银行</t>
-  </si>
-  <si>
-    <t>非银金融</t>
-  </si>
-  <si>
-    <t>综合</t>
-  </si>
-  <si>
-    <t>建筑材料</t>
-  </si>
-  <si>
-    <t>建筑装饰</t>
-  </si>
-  <si>
-    <t>电力设备</t>
-  </si>
-  <si>
-    <t>机械设备</t>
-  </si>
-  <si>
-    <t>国防军工</t>
-  </si>
-  <si>
-    <t>计算机</t>
-  </si>
-  <si>
-    <t>传媒</t>
-  </si>
-  <si>
-    <t>通信</t>
-  </si>
-  <si>
-    <t>煤炭</t>
-  </si>
-  <si>
-    <t>石油石化</t>
-  </si>
-  <si>
-    <t>环保</t>
-  </si>
-  <si>
-    <t>美容护理</t>
-  </si>
-  <si>
-    <t>2024Q1</t>
-  </si>
-  <si>
-    <t>2024Q2</t>
-  </si>
-  <si>
-    <t>2024Q3</t>
-  </si>
-  <si>
-    <t>2024Q4</t>
-  </si>
-  <si>
-    <t>2025Q1</t>
-  </si>
-  <si>
-    <t>2025Q2</t>
-  </si>
-  <si>
-    <t>2025Q3</t>
-  </si>
-  <si>
-    <t>2025Q4</t>
-  </si>
-  <si>
-    <t>2026Q1</t>
-  </si>
-  <si>
-    <t>2026Q2</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -176,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -470,1089 +408,1277 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:32">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>31</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>基础化工</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>钢铁</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>有色金属</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>家用电器</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>纺织服饰</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>轻工制造</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>商贸零售</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>社会服务</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>非银金融</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>建筑材料</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>建筑装饰</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>国防军工</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>传媒</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>通信</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>石油石化</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>环保</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>美容护理</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:32">
-      <c r="A2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0.3971843015570062</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>0.6158908393107927</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>-0.2041028108119614</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>2.055479850170468</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>4.017360199934542</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>1.569606153222121</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>0.628340204793874</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>1.533594169642253</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>0.6129615267107966</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>0.9234094880546662</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>5.449866875179036</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>-1.439130812224047</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>-0.9126665248712031</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>-0.2511720473626573</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>0.07925119135977704</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>0.4851796419949673</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>-10.13946392167003</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>-8.514098013598234</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>0.1106349574448157</v>
       </c>
-      <c r="U2">
+      <c r="U2" t="n">
         <v>-0.3909068319481774</v>
       </c>
-      <c r="V2">
+      <c r="V2" t="n">
         <v>-1.671622179806093</v>
       </c>
-      <c r="W2">
+      <c r="W2" t="n">
         <v>2.725649084872435</v>
       </c>
-      <c r="X2">
+      <c r="X2" t="n">
         <v>1.506602070573206</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" t="n">
         <v>0.721658686135203</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" t="n">
         <v>-0.1844314219709444</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" t="n">
         <v>0.3078936275176739</v>
       </c>
-      <c r="AB2">
+      <c r="AB2" t="n">
         <v>1.164254050666681</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" t="n">
         <v>-0.4582329543508339</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" t="n">
         <v>-1.068985170719971</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" t="n">
         <v>0.3034635855515401</v>
       </c>
-      <c r="AF2">
+      <c r="AF2" t="n">
         <v>0.02253218464230056</v>
       </c>
     </row>
-    <row r="3" spans="1:32">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>0.2895992295842338</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>0.5400378293165664</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>-0.08730215506213196</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>1.977085582980287</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>6.891235016252837</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>1.602178821843796</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>1.25944750236901</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>-0.6295134380464127</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>0.4330980025121048</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>0.7108043631643354</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>5.140975167328125</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>-1.795334074920286</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>-1.426661874971756</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>-0.04608796556534722</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>-0.1202515950280302</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>0.4225103649949059</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>-10.40701588959933</v>
       </c>
-      <c r="S3">
+      <c r="S3" t="n">
         <v>-8.314544680948442</v>
       </c>
-      <c r="T3">
+      <c r="T3" t="n">
         <v>0.09297329635566971</v>
       </c>
-      <c r="U3">
+      <c r="U3" t="n">
         <v>-0.295308446253374</v>
       </c>
-      <c r="V3">
+      <c r="V3" t="n">
         <v>-1.689079338779698</v>
       </c>
-      <c r="W3">
+      <c r="W3" t="n">
         <v>2.959133057016338</v>
       </c>
-      <c r="X3">
+      <c r="X3" t="n">
         <v>1.498195516560514</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" t="n">
         <v>1.125623231496953</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" t="n">
         <v>-1.203540510524578</v>
       </c>
-      <c r="AA3">
+      <c r="AA3" t="n">
         <v>-0.03010050863272562</v>
       </c>
-      <c r="AB3">
+      <c r="AB3" t="n">
         <v>2.01915037828189</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" t="n">
         <v>-0.420563614459365</v>
       </c>
-      <c r="AD3">
+      <c r="AD3" t="n">
         <v>-0.8428443490244826</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" t="n">
         <v>0.3148346591619102</v>
       </c>
-      <c r="AF3">
+      <c r="AF3" t="n">
         <v>0.0292664225964806</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>-0.2063737849757914</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>0.2347403119150502</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>-0.2458959967841989</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>1.377915389370772</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>4.802404995170985</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>2.076207399497767</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>1.195417644857957</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>-2.112557375176797</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>0.489275353063149</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>0.7203620675484514</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>4.414025165229384</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>-2.011940907229758</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>-1.358469601017737</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>0.5454844725151944</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>0.6204167471402087</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>1.726804248780307</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>-9.687000325118369</v>
       </c>
-      <c r="S4">
+      <c r="S4" t="n">
         <v>-9.080187268720389</v>
       </c>
-      <c r="T4">
+      <c r="T4" t="n">
         <v>0.09740559625322764</v>
       </c>
-      <c r="U4">
+      <c r="U4" t="n">
         <v>-0.2986712572835103</v>
       </c>
-      <c r="V4">
+      <c r="V4" t="n">
         <v>-1.580300740145521</v>
       </c>
-      <c r="W4">
+      <c r="W4" t="n">
         <v>2.997138021581939</v>
       </c>
-      <c r="X4">
+      <c r="X4" t="n">
         <v>0.6854437997166265</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" t="n">
         <v>1.092667849143876</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" t="n">
         <v>-1.37358449388389</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" t="n">
         <v>2.929753939064135</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" t="n">
         <v>2.485568661753114</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" t="n">
         <v>-0.5705068955733026</v>
       </c>
-      <c r="AD4">
+      <c r="AD4" t="n">
         <v>-0.3126218618464134</v>
       </c>
-      <c r="AE4">
+      <c r="AE4" t="n">
         <v>0.3070401033487868</v>
       </c>
-      <c r="AF4">
+      <c r="AF4" t="n">
         <v>0.04103874180474337</v>
       </c>
     </row>
-    <row r="5" spans="1:32">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024Q4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>-0.1915588445906089</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>0.4248967010969267</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>-0.1541703890921648</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>-0.3563384782597234</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>6.833315421228674</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>2.219106674406857</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>1.059889062323652</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>-1.706671599989016</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>0.6018490086735001</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>0.9957661556103063</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>3.658303598477567</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>-2.258996973379499</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>-1.467601674418738</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>0.2413429712386419</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>0.8452978850272469</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>1.610454961151786</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>-9.290013063722306</v>
       </c>
-      <c r="S5">
+      <c r="S5" t="n">
         <v>-9.914680876142647</v>
       </c>
-      <c r="T5">
+      <c r="T5" t="n">
         <v>0.118802413956014</v>
       </c>
-      <c r="U5">
+      <c r="U5" t="n">
         <v>-0.1943609244165603</v>
       </c>
-      <c r="V5">
+      <c r="V5" t="n">
         <v>-1.388955170069795</v>
       </c>
-      <c r="W5">
+      <c r="W5" t="n">
         <v>3.449227915756</v>
       </c>
-      <c r="X5">
+      <c r="X5" t="n">
         <v>0.9597207491993762</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" t="n">
         <v>1.09063872813066</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" t="n">
         <v>-1.115928293710437</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" t="n">
         <v>3.074796343303386</v>
       </c>
-      <c r="AB5">
+      <c r="AB5" t="n">
         <v>1.307805315686787</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" t="n">
         <v>-0.7532172591110148</v>
       </c>
-      <c r="AD5">
+      <c r="AD5" t="n">
         <v>-0.2551674024766515</v>
       </c>
-      <c r="AE5">
+      <c r="AE5" t="n">
         <v>0.3666884502301383</v>
       </c>
-      <c r="AF5">
+      <c r="AF5" t="n">
         <v>0.1847585938816299</v>
       </c>
     </row>
-    <row r="6" spans="1:32">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>-0.3566647147308262</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>0.1927449496013538</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>-0.1186725521251005</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>0.1535279799739921</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>8.136820772917165</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>3.004417015777614</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>0.4797742858419558</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>-1.917503240720778</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>0.4742900084757767</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>1.023903014927147</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>4.150797740200217</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>-2.50868188847025</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>-1.845176305348146</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>0.1728280743698076</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>2.273775678883694</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>1.269547792596928</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>-10.00972571882913</v>
       </c>
-      <c r="S6">
+      <c r="S6" t="n">
         <v>-9.575931861992965</v>
       </c>
-      <c r="T6">
+      <c r="T6" t="n">
         <v>0.0896470284456255</v>
       </c>
-      <c r="U6">
+      <c r="U6" t="n">
         <v>-0.1899074414989692</v>
       </c>
-      <c r="V6">
+      <c r="V6" t="n">
         <v>-1.346072497256721</v>
       </c>
-      <c r="W6">
+      <c r="W6" t="n">
         <v>1.461916398624886</v>
       </c>
-      <c r="X6">
+      <c r="X6" t="n">
         <v>1.156280719804967</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" t="n">
         <v>0.769847363221432</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" t="n">
         <v>-1.161088631353663</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" t="n">
         <v>4.986487375004888</v>
       </c>
-      <c r="AB6">
+      <c r="AB6" t="n">
         <v>0.2002413220906338</v>
       </c>
-      <c r="AC6">
+      <c r="AC6" t="n">
         <v>-0.941835319949615</v>
       </c>
-      <c r="AD6">
+      <c r="AD6" t="n">
         <v>-0.6404543746773398</v>
       </c>
-      <c r="AE6">
+      <c r="AE6" t="n">
         <v>0.3054408586413481</v>
       </c>
-      <c r="AF6">
+      <c r="AF6" t="n">
         <v>0.3114261675540734</v>
       </c>
     </row>
-    <row r="7" spans="1:32">
-      <c r="A7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>0.04369161408362743</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>0.6664534493891405</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>-0.2697617093121585</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>0.1013774310845843</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>8.144804916355566</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>1.731406459884074</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>0.2773987428200275</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>-3.393686421745921</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>0.5615520033811108</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>1.565252598280312</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>6.287290751358881</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>-2.703783397060826</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>-1.859407065670305</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>0.1082991635267633</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>1.393074417298089</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>0.9212056476492289</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>-10.83202827249227</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>-9.086658498541011</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>0.1464716133732517</v>
       </c>
-      <c r="U7">
+      <c r="U7" t="n">
         <v>0.003137504565668192</v>
       </c>
-      <c r="V7">
+      <c r="V7" t="n">
         <v>-1.427736093671489</v>
       </c>
-      <c r="W7">
+      <c r="W7" t="n">
         <v>1.249588757690483</v>
       </c>
-      <c r="X7">
+      <c r="X7" t="n">
         <v>0.9339600719076122</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" t="n">
         <v>1.287265170542823</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" t="n">
         <v>-1.631714072601559</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" t="n">
         <v>4.919855119558901</v>
       </c>
-      <c r="AB7">
+      <c r="AB7" t="n">
         <v>1.929407197679871</v>
       </c>
-      <c r="AC7">
+      <c r="AC7" t="n">
         <v>-0.993585841910388</v>
       </c>
-      <c r="AD7">
+      <c r="AD7" t="n">
         <v>-0.7923290855022839</v>
       </c>
-      <c r="AE7">
+      <c r="AE7" t="n">
         <v>0.31485503591042</v>
       </c>
-      <c r="AF7">
+      <c r="AF7" t="n">
         <v>0.4033427921677717</v>
       </c>
     </row>
-    <row r="8" spans="1:32">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>-0.1771287884177679</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>0.6032775557790426</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>-0.2088462296645049</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>0.5113281917448527</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>12.24027905739986</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>0.7863657985088413</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>-0.389834999067892</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>-3.134259395035008</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>0.1784695685137243</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>0.3888142701825859</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>4.169371732877162</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>-2.540428930550916</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>-1.867862730390658</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>-0.09020456472529814</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>0.07403643419211547</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>0.2173209137218273</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>-9.890535703177971</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>-8.617748293336325</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>0.08136601882646417</v>
       </c>
-      <c r="U8">
+      <c r="U8" t="n">
         <v>0.1428978887740481</v>
       </c>
-      <c r="V8">
+      <c r="V8" t="n">
         <v>-1.252427622435224</v>
       </c>
-      <c r="W8">
+      <c r="W8" t="n">
         <v>3.184260329997825</v>
       </c>
-      <c r="X8">
+      <c r="X8" t="n">
         <v>1.786818548357612</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" t="n">
         <v>1.009492052479389</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" t="n">
         <v>-1.833691757113717</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" t="n">
         <v>1.795557282737094</v>
       </c>
-      <c r="AB8">
+      <c r="AB8" t="n">
         <v>4.277420370632152</v>
       </c>
-      <c r="AC8">
+      <c r="AC8" t="n">
         <v>-0.8512854796990035</v>
       </c>
-      <c r="AD8">
+      <c r="AD8" t="n">
         <v>-0.9547909197734247</v>
       </c>
-      <c r="AE8">
+      <c r="AE8" t="n">
         <v>0.2106666077357423</v>
       </c>
-      <c r="AF8">
+      <c r="AF8" t="n">
         <v>0.1523027909273688</v>
       </c>
     </row>
-    <row r="9" spans="1:32">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>-0.1653478090463798</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>1.309310380599896</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>-0.07597018548731571</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>1.49060793586017</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>10.25352935589194</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>1.549645036247671</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>-0.6829392169109125</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>-2.849156610463742</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>0.1658542530718783</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>0.5864786410139124</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>3.642338510233934</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>-2.586602351281481</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>-1.740308762383081</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>-0.2793400708185336</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>0.08079896824996846</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>0.28120792538376</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>-10.03735824444476</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>-8.067572000395867</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>0.1010291010019267</v>
       </c>
-      <c r="U9">
+      <c r="U9" t="n">
         <v>0.266754693712057</v>
       </c>
-      <c r="V9">
+      <c r="V9" t="n">
         <v>-1.099815397484167</v>
       </c>
-      <c r="W9">
+      <c r="W9" t="n">
         <v>3.203397683810895</v>
       </c>
-      <c r="X9">
+      <c r="X9" t="n">
         <v>2.550514481581728</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" t="n">
         <v>0.4301358907249431</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" t="n">
         <v>-1.989695423271933</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" t="n">
         <v>0.6516294194053758</v>
       </c>
-      <c r="AB9">
+      <c r="AB9" t="n">
         <v>4.474601361358415</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" t="n">
         <v>-0.7754799545153566</v>
       </c>
-      <c r="AD9">
+      <c r="AD9" t="n">
         <v>-1.007651959142146</v>
       </c>
-      <c r="AE9">
+      <c r="AE9" t="n">
         <v>0.2526175585588191</v>
       </c>
-      <c r="AF9">
+      <c r="AF9" t="n">
         <v>0.0697867889383977</v>
       </c>
     </row>
-    <row r="10" spans="1:32">
-      <c r="A10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>-0.1730796599505614</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>2.047820542282768</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>0.001890942832943998</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>0.3937406911658012</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>9.082275084060822</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>0.5207212872141032</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>-1.132556964676611</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>-3.131492873192859</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>0.1800772617991863</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>0.5025672240305954</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>4.023295605258325</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>-2.699616880854154</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>-1.497666524377651</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>-0.1981125178756792</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>-0.001063737821166644</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>0.2908871052779538</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>-9.912564690375536</v>
       </c>
-      <c r="S10">
+      <c r="S10" t="n">
         <v>-7.69202941010389</v>
       </c>
-      <c r="T10">
+      <c r="T10" t="n">
         <v>0.07515685126483083</v>
       </c>
-      <c r="U10">
+      <c r="U10" t="n">
         <v>0.3358947631912109</v>
       </c>
-      <c r="V10">
+      <c r="V10" t="n">
         <v>-1.088953265651983</v>
       </c>
-      <c r="W10">
+      <c r="W10" t="n">
         <v>3.500508804522703</v>
       </c>
-      <c r="X10">
+      <c r="X10" t="n">
         <v>2.806720970163895</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" t="n">
         <v>0.3614559525858609</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" t="n">
         <v>-1.876196906451565</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" t="n">
         <v>0.3348197366751424</v>
       </c>
-      <c r="AB10">
+      <c r="AB10" t="n">
         <v>6.054968398578966</v>
       </c>
-      <c r="AC10">
+      <c r="AC10" t="n">
         <v>-0.8146078387399811</v>
       </c>
-      <c r="AD10">
+      <c r="AD10" t="n">
         <v>-0.594307180750191</v>
       </c>
-      <c r="AE10">
+      <c r="AE10" t="n">
         <v>0.247839147506882</v>
       </c>
-      <c r="AF10">
+      <c r="AF10" t="n">
         <v>0.05560808240983649</v>
       </c>
     </row>
-    <row r="11" spans="1:32">
-      <c r="A11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>-0.3023936924606953</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>0.3633288085942583</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>-0.2674623908882688</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>-1.655825780945662</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>19.02956375677275</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>-0.6870651787886242</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>-1.384753662457412</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>-3.193956715729904</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>0.1347611688257417</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>0.2932883236966882</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>1.974670013473375</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>-2.264635358456403</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>-1.711745675761532</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>-0.07919581678720053</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>-0.1523976002814152</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>0.1170409912281372</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>-8.240457737826235</v>
       </c>
-      <c r="S11">
+      <c r="S11" t="n">
         <v>-6.853282519904784</v>
       </c>
-      <c r="T11">
+      <c r="T11" t="n">
         <v>0.03968223114278481</v>
       </c>
-      <c r="U11">
+      <c r="U11" t="n">
         <v>1.017450105362553</v>
       </c>
-      <c r="V11">
+      <c r="V11" t="n">
         <v>-0.9561069858132125</v>
       </c>
-      <c r="W11">
+      <c r="W11" t="n">
         <v>-0.7580014568543456</v>
       </c>
-      <c r="X11">
+      <c r="X11" t="n">
         <v>3.291265426798284</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" t="n">
         <v>-0.3012230206333508</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" t="n">
         <v>-1.879973287726527</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" t="n">
         <v>-0.5552493183150704</v>
       </c>
-      <c r="AB11">
+      <c r="AB11" t="n">
         <v>6.096737653209759</v>
       </c>
-      <c r="AC11">
+      <c r="AC11" t="n">
         <v>-0.4992667097708434</v>
       </c>
-      <c r="AD11">
+      <c r="AD11" t="n">
         <v>-0.7321885066409757</v>
       </c>
-      <c r="AE11">
+      <c r="AE11" t="n">
         <v>0.1150254361550869</v>
       </c>
-      <c r="AF11">
+      <c r="AF11" t="n">
         <v>-0.005632499216964355</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.194177</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.149166</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.323688</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.6404</v>
+      </c>
+      <c r="F12" t="n">
+        <v>17.906606</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.107737</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-1.414593</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-3.26059</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.207409</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.398284</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.055626</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-2.614619</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1.705347</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.042873</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.102056</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.148304</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-9.954689999999999</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-7.690346</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.135238</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.263928</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.987449</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.33754</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.916445</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.035298</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1.724461</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.513784</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.223752</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.165896</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.772574</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.134083</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.036368</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>